--- a/experimentos/resultados/exp_verificar_promocion_v2.xlsx
+++ b/experimentos/resultados/exp_verificar_promocion_v2.xlsx
@@ -701,7 +701,7 @@
         <v>267</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:10">
